--- a/research/traditional_assets/database/data/south_africa/south_africa_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/south_africa/south_africa_financial_svcs_non_bank_insurance.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ11"/>
+  <dimension ref="A1:AQ10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.03242</v>
+        <v>0.0323</v>
       </c>
       <c r="E2">
-        <v>0.0263</v>
+        <v>0.08900000000000001</v>
       </c>
       <c r="F2">
-        <v>0.155</v>
+        <v>0.213</v>
       </c>
       <c r="G2">
-        <v>0.0105990692057299</v>
+        <v>0.008462993242506545</v>
       </c>
       <c r="H2">
-        <v>0.008087184666481994</v>
+        <v>0.006540952259896628</v>
       </c>
       <c r="I2">
-        <v>0.006706327093079317</v>
+        <v>0.006065083121704839</v>
       </c>
       <c r="J2">
-        <v>0.006075071497053779</v>
+        <v>0.005141358918305913</v>
       </c>
       <c r="K2">
-        <v>2636.488</v>
+        <v>3005.322</v>
       </c>
       <c r="L2">
-        <v>0.2736366186725331</v>
+        <v>0.2859297124017026</v>
       </c>
       <c r="M2">
-        <v>1339.6794</v>
+        <v>1639.5476</v>
       </c>
       <c r="N2">
-        <v>0.04574576770019135</v>
+        <v>0.05839838624956861</v>
       </c>
       <c r="O2">
-        <v>0.5081302854403282</v>
+        <v>0.5455480644004203</v>
       </c>
       <c r="P2">
-        <v>1252.4904</v>
+        <v>1514.2366</v>
       </c>
       <c r="Q2">
-        <v>0.04276854214905428</v>
+        <v>0.05393498416272483</v>
       </c>
       <c r="R2">
-        <v>0.4750601557829962</v>
+        <v>0.5038517004167938</v>
       </c>
       <c r="S2">
-        <v>87.18899999999999</v>
+        <v>125.311</v>
       </c>
       <c r="T2">
-        <v>0.06508198901916383</v>
+        <v>0.07643022990000414</v>
       </c>
       <c r="U2">
-        <v>13040.685</v>
+        <v>13422.863</v>
       </c>
       <c r="V2">
-        <v>0.4452976933595977</v>
+        <v>0.4781035561572249</v>
       </c>
       <c r="W2">
-        <v>0.2096171802054155</v>
+        <v>0.1516364236225668</v>
       </c>
       <c r="X2">
-        <v>0.03971193527481884</v>
+        <v>0.06871394478946177</v>
       </c>
       <c r="Y2">
-        <v>0.1699052449305967</v>
+        <v>0.08292247883310502</v>
       </c>
       <c r="Z2">
-        <v>0.2325431100463355</v>
+        <v>0.2748638720185587</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>0.000153955920978966</v>
       </c>
       <c r="AB2">
-        <v>0.04144163018728571</v>
+        <v>0.06616881350425105</v>
       </c>
       <c r="AC2">
-        <v>-0.04144163018728571</v>
+        <v>-0.06463817430177314</v>
       </c>
       <c r="AD2">
-        <v>34368.81</v>
+        <v>28188.07</v>
       </c>
       <c r="AE2">
-        <v>1.322792885810367</v>
+        <v>0.5635935126535413</v>
       </c>
       <c r="AF2">
-        <v>34370.13279288581</v>
+        <v>28188.63359351266</v>
       </c>
       <c r="AG2">
-        <v>21329.44779288581</v>
+        <v>14765.77059351266</v>
       </c>
       <c r="AH2">
-        <v>0.539940128061852</v>
+        <v>0.5010078637015898</v>
       </c>
       <c r="AI2">
-        <v>0.6258699649463618</v>
+        <v>0.6049266342171</v>
       </c>
       <c r="AJ2">
-        <v>0.4214076077869786</v>
+        <v>0.3446645384311929</v>
       </c>
       <c r="AK2">
-        <v>0.509358879398206</v>
+        <v>0.4450796272483718</v>
       </c>
       <c r="AL2">
-        <v>144.06</v>
+        <v>157.957</v>
       </c>
       <c r="AM2">
-        <v>8.488</v>
+        <v>5.144000000000005</v>
       </c>
       <c r="AN2">
-        <v>428.3785367069675</v>
+        <v>388.6347906412431</v>
       </c>
       <c r="AO2">
-        <v>0.4411356379286408</v>
+        <v>0.4004254322378876</v>
       </c>
       <c r="AP2">
-        <v>265.8537678285655</v>
+        <v>203.578753822678</v>
       </c>
       <c r="AQ2">
-        <v>7.487040527803958</v>
+        <v>12.29587869362363</v>
       </c>
     </row>
     <row r="3">
@@ -724,116 +724,122 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D3">
+        <v>0.203</v>
+      </c>
+      <c r="E3">
+        <v>0.0969</v>
+      </c>
       <c r="G3">
-        <v>0.2604651162790698</v>
+        <v>0.1922535211267606</v>
       </c>
       <c r="H3">
-        <v>0.2604651162790698</v>
+        <v>0.1922535211267606</v>
       </c>
       <c r="I3">
-        <v>0.2674418604651163</v>
+        <v>0.2011737089201878</v>
       </c>
       <c r="J3">
-        <v>0.2674418604651163</v>
+        <v>0.1286141513684792</v>
       </c>
       <c r="K3">
-        <v>1.65</v>
+        <v>3.42</v>
       </c>
       <c r="L3">
-        <v>0.03837209302325581</v>
+        <v>0.08028169014084506</v>
       </c>
       <c r="M3">
-        <v>1.628</v>
+        <v>2.309</v>
       </c>
       <c r="N3">
-        <v>0.05355263157894737</v>
+        <v>0.08880769230769231</v>
       </c>
       <c r="O3">
-        <v>0.9866666666666667</v>
+        <v>0.6751461988304094</v>
       </c>
       <c r="P3">
-        <v>1.39</v>
+        <v>1.91</v>
       </c>
       <c r="Q3">
-        <v>0.04572368421052631</v>
+        <v>0.07346153846153845</v>
       </c>
       <c r="R3">
-        <v>0.8424242424242424</v>
+        <v>0.5584795321637427</v>
       </c>
       <c r="S3">
-        <v>0.238</v>
+        <v>0.3990000000000002</v>
       </c>
       <c r="T3">
-        <v>0.1461916461916462</v>
+        <v>0.172802078822001</v>
       </c>
       <c r="U3">
-        <v>15.1</v>
+        <v>12.4</v>
       </c>
       <c r="V3">
-        <v>0.4967105263157895</v>
+        <v>0.4769230769230769</v>
       </c>
       <c r="W3">
-        <v>0.05409836065573771</v>
+        <v>0.1628571428571429</v>
       </c>
       <c r="X3">
-        <v>0.03078652759640112</v>
+        <v>0.05853679656040371</v>
       </c>
       <c r="Y3">
-        <v>0.02331183305933658</v>
+        <v>0.1043203462967392</v>
       </c>
       <c r="Z3">
-        <v>2.179422199695895</v>
+        <v>16.90476190476192</v>
       </c>
       <c r="AA3">
-        <v>0.5828687278256462</v>
+        <v>2.17419160646715</v>
       </c>
       <c r="AB3">
-        <v>0.03211021358541814</v>
+        <v>0.05895818098563176</v>
       </c>
       <c r="AC3">
-        <v>0.5507585142402281</v>
+        <v>2.115233425481518</v>
       </c>
       <c r="AD3">
-        <v>6.26</v>
+        <v>4.48</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>6.26</v>
+        <v>4.48</v>
       </c>
       <c r="AG3">
-        <v>-8.84</v>
+        <v>-7.92</v>
       </c>
       <c r="AH3">
-        <v>0.1707583196944899</v>
+        <v>0.146981627296588</v>
       </c>
       <c r="AI3">
-        <v>0.1989828353464717</v>
+        <v>0.1595441595441595</v>
       </c>
       <c r="AJ3">
-        <v>-0.4100185528756958</v>
+        <v>-0.4380530973451328</v>
       </c>
       <c r="AK3">
-        <v>-0.5403422982885085</v>
+        <v>-0.5051020408163265</v>
       </c>
       <c r="AL3">
-        <v>0.46</v>
+        <v>0.357</v>
       </c>
       <c r="AM3">
-        <v>0.08800000000000002</v>
+        <v>-0.126</v>
       </c>
       <c r="AN3">
-        <v>0.5008</v>
+        <v>0.479144385026738</v>
       </c>
       <c r="AO3">
-        <v>25</v>
+        <v>24.00560224089636</v>
       </c>
       <c r="AP3">
-        <v>-0.7071999999999999</v>
+        <v>-0.8470588235294118</v>
       </c>
       <c r="AQ3">
-        <v>130.6818181818182</v>
+        <v>-68.01587301587301</v>
       </c>
     </row>
     <row r="4">
@@ -853,121 +859,121 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.00744</v>
+        <v>0.0323</v>
       </c>
       <c r="E4">
-        <v>-0.0818</v>
+        <v>-0.00125</v>
       </c>
       <c r="G4">
-        <v>0.5</v>
+        <v>0.4561728395061729</v>
       </c>
       <c r="H4">
-        <v>0.3566350710900474</v>
+        <v>0.3314814814814815</v>
       </c>
       <c r="I4">
-        <v>0.2873222748815166</v>
+        <v>0.3382716049382716</v>
       </c>
       <c r="J4">
-        <v>0.2083317459349903</v>
+        <v>0.2461048488101628</v>
       </c>
       <c r="K4">
-        <v>44.9</v>
+        <v>50.2</v>
       </c>
       <c r="L4">
-        <v>0.2659952606635071</v>
+        <v>0.3098765432098766</v>
       </c>
       <c r="M4">
-        <v>37.77</v>
+        <v>47.96</v>
       </c>
       <c r="N4">
-        <v>0.06293951008165305</v>
+        <v>0.08790322580645162</v>
       </c>
       <c r="O4">
-        <v>0.8412026726057906</v>
+        <v>0.9553784860557769</v>
       </c>
       <c r="P4">
-        <v>32.8</v>
+        <v>44</v>
       </c>
       <c r="Q4">
-        <v>0.05465755707382102</v>
+        <v>0.08064516129032258</v>
       </c>
       <c r="R4">
-        <v>0.7305122494432071</v>
+        <v>0.8764940239043825</v>
       </c>
       <c r="S4">
-        <v>4.969999999999999</v>
+        <v>3.960000000000001</v>
       </c>
       <c r="T4">
-        <v>0.1315859147471538</v>
+        <v>0.08256880733944956</v>
       </c>
       <c r="U4">
-        <v>144</v>
+        <v>125.1</v>
       </c>
       <c r="V4">
-        <v>0.2399600066655557</v>
+        <v>0.2292888563049853</v>
       </c>
       <c r="W4">
-        <v>0.2096171802054155</v>
+        <v>0.1892197512250283</v>
       </c>
       <c r="X4">
-        <v>0.02908070735311833</v>
+        <v>0.05665529665466779</v>
       </c>
       <c r="Y4">
-        <v>0.1805364728522972</v>
+        <v>0.1325644545703605</v>
       </c>
       <c r="Z4">
-        <v>1.598484848484849</v>
+        <v>1.150568181818182</v>
       </c>
       <c r="AA4">
-        <v>0.333015139335477</v>
+        <v>0.2831604084321475</v>
       </c>
       <c r="AB4">
-        <v>0.02927371824126875</v>
+        <v>0.05677243677156972</v>
       </c>
       <c r="AC4">
-        <v>0.3037414210942083</v>
+        <v>0.2263879716605778</v>
       </c>
       <c r="AD4">
-        <v>19.5</v>
+        <v>13.8</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>19.5</v>
+        <v>13.8</v>
       </c>
       <c r="AG4">
-        <v>-124.5</v>
+        <v>-111.3</v>
       </c>
       <c r="AH4">
-        <v>0.03147191736604261</v>
+        <v>0.02466928852341795</v>
       </c>
       <c r="AI4">
-        <v>0.0684691011235955</v>
+        <v>0.05548854041013269</v>
       </c>
       <c r="AJ4">
-        <v>-0.2617746005046257</v>
+        <v>-0.2562744646557679</v>
       </c>
       <c r="AK4">
-        <v>-0.8842329545454545</v>
+        <v>-0.9004854368932038</v>
       </c>
       <c r="AL4">
-        <v>123.7</v>
+        <v>137.9</v>
       </c>
       <c r="AM4">
-        <v>-11.49999999999999</v>
+        <v>-10.09999999999999</v>
       </c>
       <c r="AN4">
-        <v>0.3591160220994475</v>
+        <v>0.2346938775510204</v>
       </c>
       <c r="AO4">
-        <v>0.3920776071139854</v>
+        <v>0.397389412617839</v>
       </c>
       <c r="AP4">
-        <v>-2.292817679558011</v>
+        <v>-1.892857142857143</v>
       </c>
       <c r="AQ4">
-        <v>-4.217391304347831</v>
+        <v>-5.425742574257429</v>
       </c>
     </row>
     <row r="5">
@@ -987,118 +993,118 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.162</v>
+        <v>-0.0379</v>
       </c>
       <c r="G5">
-        <v>0.05433333333333333</v>
+        <v>0.06718903036238982</v>
       </c>
       <c r="H5">
-        <v>0.05433333333333333</v>
+        <v>0.06718903036238982</v>
       </c>
       <c r="I5">
-        <v>0.08749999999999999</v>
+        <v>0.01733594515181195</v>
       </c>
       <c r="J5">
-        <v>0.08749999999999999</v>
+        <v>0.01733594515181195</v>
       </c>
       <c r="K5">
-        <v>-14.4</v>
+        <v>-16.5</v>
       </c>
       <c r="L5">
-        <v>-0.12</v>
+        <v>-0.1616062683643487</v>
       </c>
       <c r="M5">
-        <v>6.251</v>
+        <v>2.099</v>
       </c>
       <c r="N5">
-        <v>0.1179433962264151</v>
+        <v>0.1249404761904762</v>
       </c>
       <c r="O5">
-        <v>-0.4340972222222222</v>
+        <v>-0.1272121212121212</v>
       </c>
       <c r="P5">
-        <v>5.91</v>
+        <v>1.58</v>
       </c>
       <c r="Q5">
-        <v>0.1115094339622641</v>
+        <v>0.09404761904761905</v>
       </c>
       <c r="R5">
-        <v>-0.4104166666666667</v>
+        <v>-0.09575757575757576</v>
       </c>
       <c r="S5">
-        <v>0.3410000000000002</v>
+        <v>0.5190000000000001</v>
       </c>
       <c r="T5">
-        <v>0.05455127179651258</v>
+        <v>0.2472606002858505</v>
       </c>
       <c r="U5">
-        <v>52.5</v>
+        <v>39.6</v>
       </c>
       <c r="V5">
-        <v>0.9905660377358491</v>
+        <v>2.357142857142857</v>
       </c>
       <c r="W5">
-        <v>-0.1773399014778325</v>
+        <v>-0.2546296296296297</v>
       </c>
       <c r="X5">
-        <v>0.05728544928890528</v>
+        <v>0.1872070134013831</v>
       </c>
       <c r="Y5">
-        <v>-0.2346253507667378</v>
+        <v>-0.4418366430310128</v>
       </c>
       <c r="Z5">
-        <v>2.424242424242424</v>
+        <v>0.9542056074766354</v>
       </c>
       <c r="AA5">
-        <v>0.2121212121212121</v>
+        <v>0.01654205607476636</v>
       </c>
       <c r="AB5">
-        <v>0.04334528904603784</v>
+        <v>0.0777302437147019</v>
       </c>
       <c r="AC5">
-        <v>0.1687759230751743</v>
+        <v>-0.06118818763993554</v>
       </c>
       <c r="AD5">
-        <v>153.7</v>
+        <v>171.8</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>153.7</v>
+        <v>171.8</v>
       </c>
       <c r="AG5">
-        <v>101.2</v>
+        <v>132.2</v>
       </c>
       <c r="AH5">
-        <v>0.7435897435897436</v>
+        <v>0.9109225874867444</v>
       </c>
       <c r="AI5">
-        <v>0.6639308855291576</v>
+        <v>0.7164303586321935</v>
       </c>
       <c r="AJ5">
-        <v>0.6562905317769131</v>
+        <v>0.8872483221476509</v>
       </c>
       <c r="AK5">
-        <v>0.5653631284916201</v>
+        <v>0.6603396603396604</v>
       </c>
       <c r="AL5">
-        <v>19.9</v>
+        <v>19.7</v>
       </c>
       <c r="AM5">
-        <v>19.9</v>
+        <v>19.7</v>
       </c>
       <c r="AN5">
-        <v>12.70247933884298</v>
+        <v>45.57029177718833</v>
       </c>
       <c r="AO5">
-        <v>0.5276381909547739</v>
+        <v>0.08984771573604061</v>
       </c>
       <c r="AP5">
-        <v>8.363636363636363</v>
+        <v>35.06631299734748</v>
       </c>
       <c r="AQ5">
-        <v>0.5276381909547739</v>
+        <v>0.08984771573604061</v>
       </c>
     </row>
     <row r="6">
@@ -1109,7 +1115,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Transaction Capital Limited (JSE:TCP)</t>
+          <t>RMB Holdings Limited (JSE:RMH)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1117,12 +1123,6 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D6">
-        <v>0.2</v>
-      </c>
-      <c r="E6">
-        <v>0.38</v>
-      </c>
       <c r="G6">
         <v>0</v>
       </c>
@@ -1130,103 +1130,97 @@
         <v>0</v>
       </c>
       <c r="I6">
-        <v>0.00329348198713424</v>
+        <v>-0.63</v>
       </c>
       <c r="J6">
-        <v>0.002902516127611193</v>
+        <v>-0.63</v>
       </c>
       <c r="K6">
-        <v>152.6</v>
+        <v>-4.44</v>
       </c>
       <c r="L6">
-        <v>0.4717156105100463</v>
+        <v>-1.48</v>
       </c>
       <c r="M6">
-        <v>10.8</v>
+        <v>0.333</v>
       </c>
       <c r="N6">
-        <v>0.00530842958957975</v>
+        <v>0.007551020408163266</v>
       </c>
       <c r="O6">
-        <v>0.0707732634338139</v>
+        <v>-0.075</v>
       </c>
       <c r="P6">
-        <v>10.8</v>
+        <v>-0</v>
       </c>
       <c r="Q6">
-        <v>0.00530842958957975</v>
+        <v>-0</v>
       </c>
       <c r="R6">
-        <v>0.0707732634338139</v>
+        <v>0</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U6">
-        <v>149</v>
+        <v>4.94</v>
       </c>
       <c r="V6">
-        <v>0.07323666748586877</v>
+        <v>0.1120181405895692</v>
       </c>
       <c r="W6">
-        <v>0.4373746059042706</v>
+        <v>-0.01788159484494563</v>
       </c>
       <c r="X6">
-        <v>0.03426587230411104</v>
+        <v>0.05633159200320106</v>
       </c>
       <c r="Y6">
-        <v>0.4031087336001595</v>
+        <v>-0.07421318684814669</v>
       </c>
       <c r="Z6">
-        <v>0.2954276405036756</v>
+        <v>0.01244968253309541</v>
       </c>
       <c r="AA6">
-        <v>0.0008574834911040402</v>
+        <v>-0.007843299995850105</v>
       </c>
       <c r="AB6">
-        <v>0.03579897589739517</v>
+        <v>0.05633159200320106</v>
       </c>
       <c r="AC6">
-        <v>-0.03494149240629113</v>
+        <v>-0.06417489199905117</v>
       </c>
       <c r="AD6">
-        <v>1137.3</v>
+        <v>0</v>
       </c>
       <c r="AE6">
-        <v>1.322792885810367</v>
+        <v>0</v>
       </c>
       <c r="AF6">
-        <v>1138.62279288581</v>
+        <v>0</v>
       </c>
       <c r="AG6">
-        <v>989.6227928858102</v>
+        <v>-4.94</v>
       </c>
       <c r="AH6">
-        <v>0.358833511088389</v>
+        <v>0</v>
       </c>
       <c r="AI6">
-        <v>0.6051602442399502</v>
+        <v>0</v>
       </c>
       <c r="AJ6">
-        <v>0.3272429265153778</v>
+        <v>-0.1261491317671093</v>
       </c>
       <c r="AK6">
-        <v>0.5712033324753123</v>
+        <v>-0.02714882391734447</v>
       </c>
       <c r="AL6">
         <v>0</v>
       </c>
       <c r="AM6">
         <v>0</v>
-      </c>
-      <c r="AN6">
-        <v>855.1127819548872</v>
-      </c>
-      <c r="AP6">
-        <v>744.0772878840678</v>
       </c>
     </row>
     <row r="7">
@@ -1237,7 +1231,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Investec Group (JSE:INL)</t>
+          <t>Transaction Capital Limited (JSE:TCP)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1246,10 +1240,13 @@
         </is>
       </c>
       <c r="D7">
-        <v>-0.0145</v>
+        <v>0.512</v>
       </c>
       <c r="E7">
-        <v>0.0152</v>
+        <v>0.242</v>
+      </c>
+      <c r="F7">
+        <v>0.277</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1258,97 +1255,106 @@
         <v>0</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>0.0003722128165154939</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>0.0003097205321520678</v>
       </c>
       <c r="K7">
-        <v>552.5</v>
+        <v>91.2</v>
       </c>
       <c r="L7">
-        <v>0.2358490566037736</v>
+        <v>0.06812579368043624</v>
       </c>
       <c r="M7">
-        <v>248.9</v>
+        <v>26.4</v>
       </c>
       <c r="N7">
-        <v>0.04943494409025005</v>
+        <v>0.01786439301664636</v>
       </c>
       <c r="O7">
-        <v>0.450497737556561</v>
+        <v>0.2894736842105263</v>
       </c>
       <c r="P7">
-        <v>169.7</v>
+        <v>26.4</v>
       </c>
       <c r="Q7">
-        <v>0.03370474090845896</v>
+        <v>0.01786439301664636</v>
       </c>
       <c r="R7">
-        <v>0.3071493212669683</v>
+        <v>0.2894736842105263</v>
       </c>
       <c r="S7">
-        <v>79.19999999999999</v>
+        <v>0</v>
       </c>
       <c r="T7">
-        <v>0.3182000803535556</v>
+        <v>0</v>
       </c>
       <c r="U7">
-        <v>5986</v>
+        <v>82</v>
       </c>
       <c r="V7">
-        <v>1.18890146775507</v>
+        <v>0.05548788740018947</v>
       </c>
       <c r="W7">
-        <v>0.09839539812291856</v>
+        <v>0.1404157043879908</v>
       </c>
       <c r="X7">
-        <v>0.04675202279815234</v>
+        <v>0.06954502908183503</v>
       </c>
       <c r="Y7">
-        <v>0.05164337532476622</v>
+        <v>0.07087067530615572</v>
       </c>
       <c r="Z7">
-        <v>0.2252045260091712</v>
+        <v>0.9941602509153389</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>0.000307911841957932</v>
       </c>
       <c r="AB7">
-        <v>0.04144163018728571</v>
+        <v>0.06540936844645304</v>
       </c>
       <c r="AC7">
-        <v>-0.04144163018728571</v>
+        <v>-0.06510145660449511</v>
       </c>
       <c r="AD7">
-        <v>9209.299999999999</v>
+        <v>1525.2</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>0.5635935126535413</v>
       </c>
       <c r="AF7">
-        <v>9209.299999999999</v>
+        <v>1525.763593512654</v>
       </c>
       <c r="AG7">
-        <v>3223.299999999999</v>
+        <v>1443.763593512654</v>
       </c>
       <c r="AH7">
-        <v>0.6465298156442623</v>
+        <v>0.5079844478099697</v>
       </c>
       <c r="AI7">
-        <v>0.5529849043461552</v>
+        <v>0.741322797819314</v>
       </c>
       <c r="AJ7">
-        <v>0.3903150807682061</v>
+        <v>0.4941749673765575</v>
       </c>
       <c r="AK7">
-        <v>0.3021522713211721</v>
+        <v>0.7305891062117722</v>
       </c>
       <c r="AL7">
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>0</v>
+        <v>-4.33</v>
+      </c>
+      <c r="AN7">
+        <v>2496.235679214403</v>
+      </c>
+      <c r="AP7">
+        <v>2362.951871542805</v>
+      </c>
+      <c r="AQ7">
+        <v>-0</v>
       </c>
     </row>
     <row r="8">
@@ -1359,7 +1365,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Afristrat Investment Holdings Limited (JSE:ATI)</t>
+          <t>Investec Group (JSE:INL)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1367,95 +1373,104 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D8">
+        <v>-0.0183</v>
+      </c>
+      <c r="E8">
+        <v>0.08900000000000001</v>
+      </c>
       <c r="G8">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H8">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I8">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J8">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8">
-        <v>-21.5</v>
+        <v>829.8</v>
       </c>
       <c r="L8">
-        <v>2.193877551020408</v>
+        <v>0.3621682960893855</v>
       </c>
       <c r="M8">
-        <v>-0</v>
+        <v>388.5</v>
       </c>
       <c r="N8">
-        <v>-0</v>
+        <v>0.07094853720004382</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>0.4681851048445409</v>
       </c>
       <c r="P8">
-        <v>-0</v>
+        <v>268.4</v>
       </c>
       <c r="Q8">
-        <v>-0</v>
+        <v>0.04901566894335074</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>0.3234514340805013</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>120.1</v>
+      </c>
+      <c r="T8">
+        <v>0.3091377091377092</v>
       </c>
       <c r="U8">
-        <v>0.075</v>
+        <v>6493.4</v>
       </c>
       <c r="V8">
-        <v>0.002010723860589812</v>
+        <v>1.185835859600423</v>
       </c>
       <c r="W8">
-        <v>0.7190635451505017</v>
+        <v>0.1289310130515848</v>
       </c>
       <c r="X8">
-        <v>0.0432118152219368</v>
+        <v>0.07497687136078496</v>
       </c>
       <c r="Y8">
-        <v>0.6758517299285649</v>
+        <v>0.05395414169079987</v>
       </c>
       <c r="Z8">
-        <v>-0.2004499897729597</v>
+        <v>0.2400620271997653</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.04414200733154946</v>
+        <v>0.06692825856204905</v>
       </c>
       <c r="AC8">
-        <v>-0.04414200733154946</v>
+        <v>-0.06692825856204905</v>
       </c>
       <c r="AD8">
-        <v>54.8</v>
+        <v>7977.6</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>54.8</v>
+        <v>7977.6</v>
       </c>
       <c r="AG8">
-        <v>54.72499999999999</v>
+        <v>1484.200000000001</v>
       </c>
       <c r="AH8">
-        <v>0.5950054288816504</v>
+        <v>0.5929802131803112</v>
       </c>
       <c r="AI8">
-        <v>1.570200573065903</v>
+        <v>0.5576869302611711</v>
       </c>
       <c r="AJ8">
-        <v>0.5946753599565335</v>
+        <v>0.2132471264367817</v>
       </c>
       <c r="AK8">
-        <v>1.571428571428571</v>
+        <v>0.190004352612848</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1481,10 +1496,10 @@
         </is>
       </c>
       <c r="D9">
-        <v>-0.224</v>
+        <v>-0.111</v>
       </c>
       <c r="G9">
-        <v>0.003407155025553663</v>
+        <v>0.00398406374501992</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -1496,10 +1511,10 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>-0.962</v>
+        <v>-0.758</v>
       </c>
       <c r="L9">
-        <v>-1.638841567291312</v>
+        <v>-1.50996015936255</v>
       </c>
       <c r="M9">
         <v>-0</v>
@@ -1523,55 +1538,55 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>0.28</v>
+        <v>0.023</v>
       </c>
       <c r="V9">
-        <v>0.877742946708464</v>
+        <v>0.03703703703703703</v>
       </c>
       <c r="W9">
-        <v>2.051172707889126</v>
+        <v>0.5191780821917809</v>
       </c>
       <c r="X9">
-        <v>0.1043039270924254</v>
+        <v>0.1117692525775745</v>
       </c>
       <c r="Y9">
-        <v>1.9468687807967</v>
+        <v>0.4074088296142063</v>
       </c>
       <c r="Z9">
-        <v>1.390995260663507</v>
+        <v>0.7070422535211266</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.04805572300565535</v>
+        <v>0.07767056804735796</v>
       </c>
       <c r="AC9">
-        <v>-0.04805572300565535</v>
+        <v>-0.07767056804735796</v>
       </c>
       <c r="AD9">
-        <v>2.45</v>
+        <v>2.69</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>2.45</v>
+        <v>2.69</v>
       </c>
       <c r="AG9">
-        <v>2.17</v>
+        <v>2.667</v>
       </c>
       <c r="AH9">
-        <v>0.8847959552184904</v>
+        <v>0.8124433705829055</v>
       </c>
       <c r="AI9">
-        <v>2.474747474747474</v>
+        <v>3.898550724637682</v>
       </c>
       <c r="AJ9">
-        <v>0.8718360787464845</v>
+        <v>0.8111313868613138</v>
       </c>
       <c r="AK9">
-        <v>3.056338028169014</v>
+        <v>3.998500749625188</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1597,13 +1612,13 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.0574</v>
+        <v>0.067</v>
       </c>
       <c r="E10">
-        <v>0.0374</v>
+        <v>0.06150000000000001</v>
       </c>
       <c r="F10">
-        <v>0.155</v>
+        <v>0.149</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1618,28 +1633,28 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>1928.2</v>
+        <v>2052.4</v>
       </c>
       <c r="L10">
-        <v>0.2899505270597434</v>
+        <v>0.3123611237938697</v>
       </c>
       <c r="M10">
-        <v>1031.8904</v>
+        <v>1171.9466</v>
       </c>
       <c r="N10">
-        <v>0.04830043063096798</v>
+        <v>0.05720021475461843</v>
       </c>
       <c r="O10">
-        <v>0.5351573488227362</v>
+        <v>0.571012765542779</v>
       </c>
       <c r="P10">
-        <v>1031.8904</v>
+        <v>1171.9466</v>
       </c>
       <c r="Q10">
-        <v>0.04830043063096798</v>
+        <v>0.05720021475461843</v>
       </c>
       <c r="R10">
-        <v>0.5351573488227362</v>
+        <v>0.571012765542779</v>
       </c>
       <c r="S10">
         <v>0</v>
@@ -1648,176 +1663,60 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>6686.4</v>
+        <v>6665.4</v>
       </c>
       <c r="V10">
-        <v>0.3129750982961992</v>
+        <v>0.3253239622227103</v>
       </c>
       <c r="W10">
-        <v>0.2335174151043937</v>
+        <v>0.1845301781106426</v>
       </c>
       <c r="X10">
-        <v>0.03971193527481884</v>
+        <v>0.0678828604970885</v>
       </c>
       <c r="Y10">
-        <v>0.1938054798295749</v>
+        <v>0.1166473176135541</v>
       </c>
       <c r="Z10">
-        <v>0.225674212782131</v>
+        <v>0.244652212280643</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.04853966764407601</v>
+        <v>0.08008145636232357</v>
       </c>
       <c r="AC10">
-        <v>-0.04853966764407601</v>
+        <v>-0.08008145636232357</v>
       </c>
       <c r="AD10">
-        <v>23785.5</v>
+        <v>18492.5</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>23785.5</v>
+        <v>18492.5</v>
       </c>
       <c r="AG10">
-        <v>17099.1</v>
+        <v>11827.1</v>
       </c>
       <c r="AH10">
-        <v>0.526816465298619</v>
+        <v>0.4743977835355686</v>
       </c>
       <c r="AI10">
-        <v>0.6690999620237141</v>
+        <v>0.6261999979682574</v>
       </c>
       <c r="AJ10">
-        <v>0.4445585509228325</v>
+        <v>0.3659873250071173</v>
       </c>
       <c r="AK10">
-        <v>0.5924412984502166</v>
+        <v>0.517237458398751</v>
       </c>
       <c r="AL10">
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>South Africa</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>RMB Holdings Limited (JSE:RMH)</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
-        </is>
-      </c>
-      <c r="G11">
-        <v>-0</v>
-      </c>
-      <c r="H11">
-        <v>-0</v>
-      </c>
-      <c r="I11">
-        <v>1.83377308707124</v>
-      </c>
-      <c r="J11">
-        <v>1.83377308707124</v>
-      </c>
-      <c r="K11">
-        <v>-6.5</v>
-      </c>
-      <c r="L11">
-        <v>1.715039577836412</v>
-      </c>
-      <c r="M11">
-        <v>2.44</v>
-      </c>
-      <c r="N11">
-        <v>0.01865443425076452</v>
-      </c>
-      <c r="O11">
-        <v>-0.3753846153846154</v>
-      </c>
-      <c r="P11">
-        <v>-0</v>
-      </c>
-      <c r="Q11">
-        <v>-0</v>
-      </c>
-      <c r="R11">
-        <v>0</v>
-      </c>
-      <c r="S11">
-        <v>2.44</v>
-      </c>
-      <c r="T11">
-        <v>1</v>
-      </c>
-      <c r="U11">
-        <v>7.33</v>
-      </c>
-      <c r="V11">
-        <v>0.05603975535168195</v>
-      </c>
-      <c r="W11">
-        <v>-0.02273522210563134</v>
-      </c>
-      <c r="X11">
-        <v>0.02876109109096674</v>
-      </c>
-      <c r="Y11">
-        <v>-0.05149631319659807</v>
-      </c>
-      <c r="Z11">
-        <v>-0.01552006552006552</v>
-      </c>
-      <c r="AA11">
-        <v>-0.02846027846027846</v>
-      </c>
-      <c r="AB11">
-        <v>0.02876109109096674</v>
-      </c>
-      <c r="AC11">
-        <v>-0.0572213695512452</v>
-      </c>
-      <c r="AD11">
-        <v>0</v>
-      </c>
-      <c r="AE11">
-        <v>0</v>
-      </c>
-      <c r="AF11">
-        <v>0</v>
-      </c>
-      <c r="AG11">
-        <v>-7.33</v>
-      </c>
-      <c r="AH11">
-        <v>0</v>
-      </c>
-      <c r="AI11">
-        <v>0</v>
-      </c>
-      <c r="AJ11">
-        <v>-0.05936664776868875</v>
-      </c>
-      <c r="AK11">
-        <v>-0.03041872432252977</v>
-      </c>
-      <c r="AL11">
-        <v>0</v>
-      </c>
-      <c r="AM11">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/south_africa/south_africa_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/south_africa/south_africa_financial_svcs_non_bank_insurance.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ10"/>
+  <dimension ref="A1:AQ12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0323</v>
+        <v>0.0345</v>
       </c>
       <c r="E2">
-        <v>0.08900000000000001</v>
+        <v>-0.0171</v>
       </c>
       <c r="F2">
-        <v>0.213</v>
+        <v>0.09859999999999999</v>
       </c>
       <c r="G2">
-        <v>0.008462993242506545</v>
+        <v>0.01155290884104443</v>
       </c>
       <c r="H2">
-        <v>0.006540952259896628</v>
+        <v>0.009650978060642685</v>
       </c>
       <c r="I2">
-        <v>0.006065083121704839</v>
+        <v>0.007338327465252867</v>
       </c>
       <c r="J2">
-        <v>0.005141358918305913</v>
+        <v>0.005991367325924301</v>
       </c>
       <c r="K2">
-        <v>3005.322</v>
+        <v>3158.595</v>
       </c>
       <c r="L2">
-        <v>0.2859297124017026</v>
+        <v>0.3078522626485122</v>
       </c>
       <c r="M2">
-        <v>1639.5476</v>
+        <v>1964.6994</v>
       </c>
       <c r="N2">
-        <v>0.05839838624956861</v>
+        <v>0.066573808255785</v>
       </c>
       <c r="O2">
-        <v>0.5455480644004203</v>
+        <v>0.6220168777573574</v>
       </c>
       <c r="P2">
-        <v>1514.2366</v>
+        <v>1530.8464</v>
       </c>
       <c r="Q2">
-        <v>0.05393498416272483</v>
+        <v>0.05187270617716824</v>
       </c>
       <c r="R2">
-        <v>0.5038517004167938</v>
+        <v>0.484660553188997</v>
       </c>
       <c r="S2">
-        <v>125.311</v>
+        <v>433.853</v>
       </c>
       <c r="T2">
-        <v>0.07643022990000414</v>
+        <v>0.2208241118208719</v>
       </c>
       <c r="U2">
-        <v>13422.863</v>
+        <v>14380.61</v>
       </c>
       <c r="V2">
-        <v>0.4781035561572249</v>
+        <v>0.4872867435808371</v>
       </c>
       <c r="W2">
-        <v>0.1516364236225668</v>
+        <v>0.109766889158576</v>
       </c>
       <c r="X2">
-        <v>0.06871394478946177</v>
+        <v>0.06941547193706417</v>
       </c>
       <c r="Y2">
-        <v>0.08292247883310502</v>
+        <v>0.04035141722151188</v>
       </c>
       <c r="Z2">
-        <v>0.2748638720185587</v>
+        <v>0.3470742015842715</v>
       </c>
       <c r="AA2">
-        <v>0.000153955920978966</v>
+        <v>0.03586133631483649</v>
       </c>
       <c r="AB2">
-        <v>0.06616881350425105</v>
+        <v>0.065684053217647</v>
       </c>
       <c r="AC2">
-        <v>-0.06463817430177314</v>
+        <v>-0.03281701696725728</v>
       </c>
       <c r="AD2">
-        <v>28188.07</v>
+        <v>26688.76</v>
       </c>
       <c r="AE2">
-        <v>0.5635935126535413</v>
+        <v>4.790131868795291</v>
       </c>
       <c r="AF2">
-        <v>28188.63359351266</v>
+        <v>26693.5501318688</v>
       </c>
       <c r="AG2">
-        <v>14765.77059351266</v>
+        <v>12312.9401318688</v>
       </c>
       <c r="AH2">
-        <v>0.5010078637015898</v>
+        <v>0.4749307046424103</v>
       </c>
       <c r="AI2">
-        <v>0.6049266342171</v>
+        <v>0.6021361384874616</v>
       </c>
       <c r="AJ2">
-        <v>0.3446645384311929</v>
+        <v>0.2943951320500515</v>
       </c>
       <c r="AK2">
-        <v>0.4450796272483718</v>
+        <v>0.4111054117620465</v>
       </c>
       <c r="AL2">
-        <v>157.957</v>
+        <v>264.5</v>
       </c>
       <c r="AM2">
-        <v>5.144000000000005</v>
+        <v>23.39400000000001</v>
       </c>
       <c r="AN2">
-        <v>388.6347906412431</v>
+        <v>246.4108577232019</v>
       </c>
       <c r="AO2">
-        <v>0.4004254322378876</v>
+        <v>0.2802646502835539</v>
       </c>
       <c r="AP2">
-        <v>203.578753822678</v>
+        <v>113.6823943483408</v>
       </c>
       <c r="AQ2">
-        <v>12.29587869362363</v>
+        <v>3.168761220825852</v>
       </c>
     </row>
     <row r="3">
@@ -725,121 +725,121 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.203</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="E3">
-        <v>0.0969</v>
+        <v>-0.0171</v>
       </c>
       <c r="G3">
-        <v>0.1922535211267606</v>
+        <v>0.194910941475827</v>
       </c>
       <c r="H3">
-        <v>0.1922535211267606</v>
+        <v>0.194910941475827</v>
       </c>
       <c r="I3">
-        <v>0.2011737089201878</v>
+        <v>0.1631043256997456</v>
       </c>
       <c r="J3">
-        <v>0.1286141513684792</v>
+        <v>0.1007694051847933</v>
       </c>
       <c r="K3">
-        <v>3.42</v>
+        <v>2.57</v>
       </c>
       <c r="L3">
-        <v>0.08028169014084506</v>
+        <v>0.06539440203562341</v>
       </c>
       <c r="M3">
-        <v>2.309</v>
+        <v>1.88</v>
       </c>
       <c r="N3">
-        <v>0.08880769230769231</v>
+        <v>0.07768595041322314</v>
       </c>
       <c r="O3">
-        <v>0.6751461988304094</v>
+        <v>0.7315175097276264</v>
       </c>
       <c r="P3">
-        <v>1.91</v>
+        <v>1.68</v>
       </c>
       <c r="Q3">
-        <v>0.07346153846153845</v>
+        <v>0.06942148760330578</v>
       </c>
       <c r="R3">
-        <v>0.5584795321637427</v>
+        <v>0.6536964980544747</v>
       </c>
       <c r="S3">
-        <v>0.3990000000000002</v>
+        <v>0.2</v>
       </c>
       <c r="T3">
-        <v>0.172802078822001</v>
+        <v>0.1063829787234042</v>
       </c>
       <c r="U3">
-        <v>12.4</v>
+        <v>9.75</v>
       </c>
       <c r="V3">
-        <v>0.4769230769230769</v>
+        <v>0.4028925619834711</v>
       </c>
       <c r="W3">
-        <v>0.1628571428571429</v>
+        <v>0.1338541666666667</v>
       </c>
       <c r="X3">
-        <v>0.05853679656040371</v>
+        <v>0.06355559701579126</v>
       </c>
       <c r="Y3">
-        <v>0.1043203462967392</v>
+        <v>0.0702985696508754</v>
       </c>
       <c r="Z3">
-        <v>16.90476190476192</v>
+        <v>12.75974025974026</v>
       </c>
       <c r="AA3">
-        <v>2.17419160646715</v>
+        <v>1.285791436286486</v>
       </c>
       <c r="AB3">
-        <v>0.05895818098563176</v>
+        <v>0.06346198041409577</v>
       </c>
       <c r="AC3">
-        <v>2.115233425481518</v>
+        <v>1.22232945587239</v>
       </c>
       <c r="AD3">
-        <v>4.48</v>
+        <v>4.92</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>4.48</v>
+        <v>4.92</v>
       </c>
       <c r="AG3">
-        <v>-7.92</v>
+        <v>-4.83</v>
       </c>
       <c r="AH3">
-        <v>0.146981627296588</v>
+        <v>0.168956043956044</v>
       </c>
       <c r="AI3">
-        <v>0.1595441595441595</v>
+        <v>0.1827637444279346</v>
       </c>
       <c r="AJ3">
-        <v>-0.4380530973451328</v>
+        <v>-0.2493546721734642</v>
       </c>
       <c r="AK3">
-        <v>-0.5051020408163265</v>
+        <v>-0.2813046010483401</v>
       </c>
       <c r="AL3">
-        <v>0.357</v>
+        <v>0.393</v>
       </c>
       <c r="AM3">
-        <v>-0.126</v>
+        <v>-0.153</v>
       </c>
       <c r="AN3">
-        <v>0.479144385026738</v>
+        <v>0.6871508379888268</v>
       </c>
       <c r="AO3">
-        <v>24.00560224089636</v>
+        <v>16.31043256997456</v>
       </c>
       <c r="AP3">
-        <v>-0.8470588235294118</v>
+        <v>-0.6745810055865922</v>
       </c>
       <c r="AQ3">
-        <v>-68.01587301587301</v>
+        <v>-41.8954248366013</v>
       </c>
     </row>
     <row r="4">
@@ -850,7 +850,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>JSE Limited (JSE:JSE)</t>
+          <t>Capital Appreciation Limited (JSE:CTA)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -859,121 +859,121 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0323</v>
+        <v>0.102</v>
       </c>
       <c r="E4">
-        <v>-0.00125</v>
+        <v>-0.0237</v>
       </c>
       <c r="G4">
-        <v>0.4561728395061729</v>
+        <v>0.155410447761194</v>
       </c>
       <c r="H4">
-        <v>0.3314814814814815</v>
+        <v>0.155410447761194</v>
       </c>
       <c r="I4">
-        <v>0.3382716049382716</v>
+        <v>0.1552238805970149</v>
       </c>
       <c r="J4">
-        <v>0.2461048488101628</v>
+        <v>0.1042217484008529</v>
       </c>
       <c r="K4">
-        <v>50.2</v>
+        <v>7.06</v>
       </c>
       <c r="L4">
-        <v>0.3098765432098766</v>
+        <v>0.1317164179104477</v>
       </c>
       <c r="M4">
-        <v>47.96</v>
+        <v>6.389</v>
       </c>
       <c r="N4">
-        <v>0.08790322580645162</v>
+        <v>0.07044101433296582</v>
       </c>
       <c r="O4">
-        <v>0.9553784860557769</v>
+        <v>0.9049575070821531</v>
       </c>
       <c r="P4">
-        <v>44</v>
+        <v>5.42</v>
       </c>
       <c r="Q4">
-        <v>0.08064516129032258</v>
+        <v>0.05975744211686879</v>
       </c>
       <c r="R4">
-        <v>0.8764940239043825</v>
+        <v>0.7677053824362606</v>
       </c>
       <c r="S4">
-        <v>3.960000000000001</v>
+        <v>0.9690000000000003</v>
       </c>
       <c r="T4">
-        <v>0.08256880733944956</v>
+        <v>0.1516669275316951</v>
       </c>
       <c r="U4">
-        <v>125.1</v>
+        <v>25.8</v>
       </c>
       <c r="V4">
-        <v>0.2292888563049853</v>
+        <v>0.2844542447629548</v>
       </c>
       <c r="W4">
-        <v>0.1892197512250283</v>
+        <v>0.08567961165048543</v>
       </c>
       <c r="X4">
-        <v>0.05665529665466779</v>
+        <v>0.06065302874677723</v>
       </c>
       <c r="Y4">
-        <v>0.1325644545703605</v>
+        <v>0.0250265829037082</v>
       </c>
       <c r="Z4">
-        <v>1.150568181818182</v>
+        <v>5.197827773467806</v>
       </c>
       <c r="AA4">
-        <v>0.2831604084321475</v>
+        <v>0.541726698437327</v>
       </c>
       <c r="AB4">
-        <v>0.05677243677156972</v>
+        <v>0.06066043257425895</v>
       </c>
       <c r="AC4">
-        <v>0.2263879716605778</v>
+        <v>0.4810662658630681</v>
       </c>
       <c r="AD4">
-        <v>13.8</v>
+        <v>1.71</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>13.8</v>
+        <v>1.71</v>
       </c>
       <c r="AG4">
-        <v>-111.3</v>
+        <v>-24.09</v>
       </c>
       <c r="AH4">
-        <v>0.02466928852341795</v>
+        <v>0.01850449085596797</v>
       </c>
       <c r="AI4">
-        <v>0.05548854041013269</v>
+        <v>0.02006806712827133</v>
       </c>
       <c r="AJ4">
-        <v>-0.2562744646557679</v>
+        <v>-0.3616574087974779</v>
       </c>
       <c r="AK4">
-        <v>-0.9004854368932038</v>
+        <v>-0.4054872917017338</v>
       </c>
       <c r="AL4">
-        <v>137.9</v>
+        <v>0.107</v>
       </c>
       <c r="AM4">
-        <v>-10.09999999999999</v>
+        <v>-2.333</v>
       </c>
       <c r="AN4">
-        <v>0.2346938775510204</v>
+        <v>0.1744897959183673</v>
       </c>
       <c r="AO4">
-        <v>0.397389412617839</v>
+        <v>77.7570093457944</v>
       </c>
       <c r="AP4">
-        <v>-1.892857142857143</v>
+        <v>-2.458163265306122</v>
       </c>
       <c r="AQ4">
-        <v>-5.425742574257429</v>
+        <v>-3.566223746249465</v>
       </c>
     </row>
     <row r="5">
@@ -984,7 +984,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Finbond Group Limited (JSE:FGL)</t>
+          <t>JSE Limited (JSE:JSE)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -993,118 +993,121 @@
         </is>
       </c>
       <c r="D5">
-        <v>-0.0379</v>
+        <v>0.0345</v>
+      </c>
+      <c r="E5">
+        <v>-0.0404</v>
       </c>
       <c r="G5">
-        <v>0.06718903036238982</v>
+        <v>0.4840499306518725</v>
       </c>
       <c r="H5">
-        <v>0.06718903036238982</v>
+        <v>0.3550624133148406</v>
       </c>
       <c r="I5">
-        <v>0.01733594515181195</v>
+        <v>0.2954230235783634</v>
       </c>
       <c r="J5">
-        <v>0.01733594515181195</v>
+        <v>0.2156894739620577</v>
       </c>
       <c r="K5">
-        <v>-16.5</v>
+        <v>42.2</v>
       </c>
       <c r="L5">
-        <v>-0.1616062683643487</v>
+        <v>0.2926490984743412</v>
       </c>
       <c r="M5">
-        <v>2.099</v>
+        <v>34.47</v>
       </c>
       <c r="N5">
-        <v>0.1249404761904762</v>
+        <v>0.07975474317445627</v>
       </c>
       <c r="O5">
-        <v>-0.1272121212121212</v>
+        <v>0.816824644549763</v>
       </c>
       <c r="P5">
-        <v>1.58</v>
+        <v>29.8</v>
       </c>
       <c r="Q5">
-        <v>0.09404761904761905</v>
+        <v>0.06894956038870893</v>
       </c>
       <c r="R5">
-        <v>-0.09575757575757576</v>
+        <v>0.7061611374407583</v>
       </c>
       <c r="S5">
-        <v>0.5190000000000001</v>
+        <v>4.669999999999998</v>
       </c>
       <c r="T5">
-        <v>0.2472606002858505</v>
+        <v>0.1354801276472294</v>
       </c>
       <c r="U5">
-        <v>39.6</v>
+        <v>100.2</v>
       </c>
       <c r="V5">
-        <v>2.357142857142857</v>
+        <v>0.2318371124479408</v>
       </c>
       <c r="W5">
-        <v>-0.2546296296296297</v>
+        <v>0.1796509152830992</v>
       </c>
       <c r="X5">
-        <v>0.1872070134013831</v>
+        <v>0.06066400896561996</v>
       </c>
       <c r="Y5">
-        <v>-0.4418366430310128</v>
+        <v>0.1189869063174792</v>
       </c>
       <c r="Z5">
-        <v>0.9542056074766354</v>
+        <v>1.166666666666666</v>
       </c>
       <c r="AA5">
-        <v>0.01654205607476636</v>
+        <v>0.2516377196224006</v>
       </c>
       <c r="AB5">
-        <v>0.0777302437147019</v>
+        <v>0.06059011091197702</v>
       </c>
       <c r="AC5">
-        <v>-0.06118818763993554</v>
+        <v>0.1910476087104236</v>
       </c>
       <c r="AD5">
-        <v>171.8</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>171.8</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="AG5">
-        <v>132.2</v>
+        <v>-91.75</v>
       </c>
       <c r="AH5">
-        <v>0.9109225874867444</v>
+        <v>0.01917621695222966</v>
       </c>
       <c r="AI5">
-        <v>0.7164303586321935</v>
+        <v>0.03786690566883263</v>
       </c>
       <c r="AJ5">
-        <v>0.8872483221476509</v>
+        <v>-0.269496254956675</v>
       </c>
       <c r="AK5">
-        <v>0.6603396603396604</v>
+        <v>-0.7462383082553884</v>
       </c>
       <c r="AL5">
-        <v>19.7</v>
+        <v>221.5</v>
       </c>
       <c r="AM5">
-        <v>19.7</v>
+        <v>-13.19999999999999</v>
       </c>
       <c r="AN5">
-        <v>45.57029177718833</v>
+        <v>0.1865342163355408</v>
       </c>
       <c r="AO5">
-        <v>0.08984771573604061</v>
+        <v>0.1923250564334086</v>
       </c>
       <c r="AP5">
-        <v>35.06631299734748</v>
+        <v>-2.025386313465784</v>
       </c>
       <c r="AQ5">
-        <v>0.08984771573604061</v>
+        <v>-3.22727272727273</v>
       </c>
     </row>
     <row r="6">
@@ -1115,7 +1118,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>RMB Holdings Limited (JSE:RMH)</t>
+          <t>Novus Holdings Limited (JSE:NVS)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1123,32 +1126,35 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D6">
+        <v>-0.028</v>
+      </c>
       <c r="G6">
-        <v>0</v>
+        <v>0.03942482341069627</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>0.03733602421796166</v>
       </c>
       <c r="I6">
-        <v>-0.63</v>
+        <v>0.04460141271442987</v>
       </c>
       <c r="J6">
-        <v>-0.63</v>
+        <v>0.03483959408259239</v>
       </c>
       <c r="K6">
-        <v>-4.44</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="L6">
-        <v>-1.48</v>
+        <v>0.04106962663975783</v>
       </c>
       <c r="M6">
-        <v>0.333</v>
+        <v>-0</v>
       </c>
       <c r="N6">
-        <v>0.007551020408163266</v>
+        <v>-0</v>
       </c>
       <c r="O6">
-        <v>-0.075</v>
+        <v>-0</v>
       </c>
       <c r="P6">
         <v>-0</v>
@@ -1157,70 +1163,79 @@
         <v>-0</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S6">
-        <v>0.333</v>
-      </c>
-      <c r="T6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U6">
-        <v>4.94</v>
+        <v>32.9</v>
       </c>
       <c r="V6">
-        <v>0.1120181405895692</v>
+        <v>0.4148802017654477</v>
       </c>
       <c r="W6">
-        <v>-0.01788159484494563</v>
+        <v>0.06892464013547842</v>
       </c>
       <c r="X6">
-        <v>0.05633159200320106</v>
+        <v>0.06531730026908282</v>
       </c>
       <c r="Y6">
-        <v>-0.07421318684814669</v>
+        <v>0.003607339866395595</v>
       </c>
       <c r="Z6">
-        <v>0.01244968253309541</v>
+        <v>1.939144897759515</v>
       </c>
       <c r="AA6">
-        <v>-0.007843299995850105</v>
+        <v>0.06755902110527162</v>
       </c>
       <c r="AB6">
-        <v>0.05633159200320106</v>
+        <v>0.06429520972314907</v>
       </c>
       <c r="AC6">
-        <v>-0.06417489199905117</v>
+        <v>0.003263811382122547</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AG6">
-        <v>-4.94</v>
+        <v>-7.899999999999999</v>
       </c>
       <c r="AH6">
-        <v>0</v>
+        <v>0.239693192713327</v>
       </c>
       <c r="AI6">
-        <v>0</v>
+        <v>0.169606512890095</v>
       </c>
       <c r="AJ6">
-        <v>-0.1261491317671093</v>
+        <v>-0.1106442577030812</v>
       </c>
       <c r="AK6">
-        <v>-0.02714882391734447</v>
+        <v>-0.06899563318777291</v>
       </c>
       <c r="AL6">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AM6">
-        <v>0</v>
+        <v>2.37</v>
+      </c>
+      <c r="AN6">
+        <v>1.689189189189189</v>
+      </c>
+      <c r="AO6">
+        <v>2.266666666666667</v>
+      </c>
+      <c r="AP6">
+        <v>-0.5337837837837837</v>
+      </c>
+      <c r="AQ6">
+        <v>3.729957805907173</v>
       </c>
     </row>
     <row r="7">
@@ -1231,7 +1246,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Transaction Capital Limited (JSE:TCP)</t>
+          <t>Finbond Group Limited (JSE:FGL)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1240,121 +1255,118 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.512</v>
-      </c>
-      <c r="E7">
-        <v>0.242</v>
-      </c>
-      <c r="F7">
-        <v>0.277</v>
+        <v>-0.0303</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>0.0847887323943662</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>0.0847887323943662</v>
       </c>
       <c r="I7">
-        <v>0.0003722128165154939</v>
+        <v>0.06544600938967136</v>
       </c>
       <c r="J7">
-        <v>0.0003097205321520678</v>
+        <v>0.06544600938967136</v>
       </c>
       <c r="K7">
-        <v>91.2</v>
+        <v>-14.4</v>
       </c>
       <c r="L7">
-        <v>0.06812579368043624</v>
+        <v>-0.1352112676056338</v>
       </c>
       <c r="M7">
-        <v>26.4</v>
+        <v>0.644</v>
       </c>
       <c r="N7">
-        <v>0.01786439301664636</v>
+        <v>0.03701149425287357</v>
       </c>
       <c r="O7">
-        <v>0.2894736842105263</v>
+        <v>-0.04472222222222223</v>
       </c>
       <c r="P7">
-        <v>26.4</v>
+        <v>-0</v>
       </c>
       <c r="Q7">
-        <v>0.01786439301664636</v>
+        <v>-0</v>
       </c>
       <c r="R7">
-        <v>0.2894736842105263</v>
+        <v>0</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>0.644</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U7">
-        <v>82</v>
+        <v>44.9</v>
       </c>
       <c r="V7">
-        <v>0.05548788740018947</v>
+        <v>2.580459770114943</v>
       </c>
       <c r="W7">
-        <v>0.1404157043879908</v>
+        <v>-0.2656826568265683</v>
       </c>
       <c r="X7">
-        <v>0.06954502908183503</v>
+        <v>0.2111157605412791</v>
       </c>
       <c r="Y7">
-        <v>0.07087067530615572</v>
+        <v>-0.4767984173678474</v>
       </c>
       <c r="Z7">
-        <v>0.9941602509153389</v>
+        <v>0.7941834451901568</v>
       </c>
       <c r="AA7">
-        <v>0.000307911841957932</v>
+        <v>0.05197613721103655</v>
       </c>
       <c r="AB7">
-        <v>0.06540936844645304</v>
+        <v>0.07700035688363124</v>
       </c>
       <c r="AC7">
-        <v>-0.06510145660449511</v>
+        <v>-0.0250242196725947</v>
       </c>
       <c r="AD7">
-        <v>1525.2</v>
+        <v>166.7</v>
       </c>
       <c r="AE7">
-        <v>0.5635935126535413</v>
+        <v>0</v>
       </c>
       <c r="AF7">
-        <v>1525.763593512654</v>
+        <v>166.7</v>
       </c>
       <c r="AG7">
-        <v>1443.763593512654</v>
+        <v>121.8</v>
       </c>
       <c r="AH7">
-        <v>0.5079844478099697</v>
+        <v>0.9054861488321564</v>
       </c>
       <c r="AI7">
-        <v>0.741322797819314</v>
+        <v>0.7363074204946997</v>
       </c>
       <c r="AJ7">
-        <v>0.4941749673765575</v>
+        <v>0.875</v>
       </c>
       <c r="AK7">
-        <v>0.7305891062117722</v>
+        <v>0.6710743801652892</v>
       </c>
       <c r="AL7">
-        <v>0</v>
+        <v>19.2</v>
       </c>
       <c r="AM7">
-        <v>-4.33</v>
+        <v>19.2</v>
       </c>
       <c r="AN7">
-        <v>2496.235679214403</v>
+        <v>18.46068660022148</v>
+      </c>
+      <c r="AO7">
+        <v>0.3630208333333333</v>
       </c>
       <c r="AP7">
-        <v>2362.951871542805</v>
+        <v>13.48837209302325</v>
       </c>
       <c r="AQ7">
-        <v>-0</v>
+        <v>0.3630208333333333</v>
       </c>
     </row>
     <row r="8">
@@ -1365,7 +1377,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Investec Group (JSE:INL)</t>
+          <t>RMB Holdings Limited (JSE:RMH)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1373,12 +1385,6 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D8">
-        <v>-0.0183</v>
-      </c>
-      <c r="E8">
-        <v>0.08900000000000001</v>
-      </c>
       <c r="G8">
         <v>0</v>
       </c>
@@ -1386,91 +1392,91 @@
         <v>0</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>1.09181141439206</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>0.8915830235173913</v>
       </c>
       <c r="K8">
-        <v>829.8</v>
+        <v>4.72</v>
       </c>
       <c r="L8">
-        <v>0.3621682960893855</v>
+        <v>1.1712158808933</v>
       </c>
       <c r="M8">
-        <v>388.5</v>
+        <v>2.97</v>
       </c>
       <c r="N8">
-        <v>0.07094853720004382</v>
+        <v>0.06098562628336756</v>
       </c>
       <c r="O8">
-        <v>0.4681851048445409</v>
+        <v>0.6292372881355933</v>
       </c>
       <c r="P8">
-        <v>268.4</v>
+        <v>-0</v>
       </c>
       <c r="Q8">
-        <v>0.04901566894335074</v>
+        <v>-0</v>
       </c>
       <c r="R8">
-        <v>0.3234514340805013</v>
+        <v>-0</v>
       </c>
       <c r="S8">
-        <v>120.1</v>
+        <v>2.97</v>
       </c>
       <c r="T8">
-        <v>0.3091377091377092</v>
+        <v>1</v>
       </c>
       <c r="U8">
-        <v>6493.4</v>
+        <v>4.45</v>
       </c>
       <c r="V8">
-        <v>1.185835859600423</v>
+        <v>0.09137577002053388</v>
       </c>
       <c r="W8">
-        <v>0.1289310130515848</v>
+        <v>0.02525414660246121</v>
       </c>
       <c r="X8">
-        <v>0.07497687136078496</v>
+        <v>0.06035634968055631</v>
       </c>
       <c r="Y8">
-        <v>0.05395414169079987</v>
+        <v>-0.0351022030780951</v>
       </c>
       <c r="Z8">
-        <v>0.2400620271997653</v>
+        <v>0.02214772477467575</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>0.01974653541863644</v>
       </c>
       <c r="AB8">
-        <v>0.06692825856204905</v>
+        <v>0.06035634968055631</v>
       </c>
       <c r="AC8">
-        <v>-0.06692825856204905</v>
+        <v>-0.04060981426191987</v>
       </c>
       <c r="AD8">
-        <v>7977.6</v>
+        <v>0</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>7977.6</v>
+        <v>0</v>
       </c>
       <c r="AG8">
-        <v>1484.200000000001</v>
+        <v>-4.45</v>
       </c>
       <c r="AH8">
-        <v>0.5929802131803112</v>
+        <v>0</v>
       </c>
       <c r="AI8">
-        <v>0.5576869302611711</v>
+        <v>0</v>
       </c>
       <c r="AJ8">
-        <v>0.2132471264367817</v>
+        <v>-0.1005649717514124</v>
       </c>
       <c r="AK8">
-        <v>0.190004352612848</v>
+        <v>-0.06150656530753283</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1487,7 +1493,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>African Dawn Capital Limited (JSE:ADW)</t>
+          <t>Investec Group (JSE:INL)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1496,10 +1502,13 @@
         </is>
       </c>
       <c r="D9">
-        <v>-0.111</v>
+        <v>-0.00787</v>
+      </c>
+      <c r="E9">
+        <v>0.12</v>
       </c>
       <c r="G9">
-        <v>0.00398406374501992</v>
+        <v>0</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -1511,82 +1520,85 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>-0.758</v>
+        <v>1149.1</v>
       </c>
       <c r="L9">
-        <v>-1.50996015936255</v>
+        <v>0.4164009276706769</v>
       </c>
       <c r="M9">
-        <v>-0</v>
+        <v>773.5</v>
       </c>
       <c r="N9">
-        <v>-0</v>
+        <v>0.1269468743332622</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>0.6731354973457488</v>
       </c>
       <c r="P9">
-        <v>-0</v>
+        <v>350.2</v>
       </c>
       <c r="Q9">
-        <v>-0</v>
+        <v>0.0574748485992352</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>0.3047602471499434</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>423.3</v>
+      </c>
+      <c r="T9">
+        <v>0.5472527472527473</v>
       </c>
       <c r="U9">
-        <v>0.023</v>
+        <v>6994.8</v>
       </c>
       <c r="V9">
-        <v>0.03703703703703703</v>
+        <v>1.147987067338465</v>
       </c>
       <c r="W9">
-        <v>0.5191780821917809</v>
+        <v>0.2063312504488975</v>
       </c>
       <c r="X9">
-        <v>0.1117692525775745</v>
+        <v>0.07966579192659348</v>
       </c>
       <c r="Y9">
-        <v>0.4074088296142063</v>
+        <v>0.126665458522304</v>
       </c>
       <c r="Z9">
-        <v>0.7070422535211266</v>
+        <v>0.3977572464290346</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.07767056804735796</v>
+        <v>0.06707289671214492</v>
       </c>
       <c r="AC9">
-        <v>-0.07767056804735796</v>
+        <v>-0.06707289671214492</v>
       </c>
       <c r="AD9">
-        <v>2.69</v>
+        <v>7476.7</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>2.69</v>
+        <v>7476.7</v>
       </c>
       <c r="AG9">
-        <v>2.667</v>
+        <v>481.8999999999996</v>
       </c>
       <c r="AH9">
-        <v>0.8124433705829055</v>
+        <v>0.5509808545446506</v>
       </c>
       <c r="AI9">
-        <v>3.898550724637682</v>
+        <v>0.5391488072918169</v>
       </c>
       <c r="AJ9">
-        <v>0.8111313868613138</v>
+        <v>0.07329277566539918</v>
       </c>
       <c r="AK9">
-        <v>3.998500749625188</v>
+        <v>0.07011698288906991</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1612,13 +1624,13 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.067</v>
+        <v>0.0738</v>
       </c>
       <c r="E10">
-        <v>0.06150000000000001</v>
+        <v>0.0677</v>
       </c>
       <c r="F10">
-        <v>0.149</v>
+        <v>0.09859999999999999</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1633,28 +1645,28 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>2052.4</v>
+        <v>1990.1</v>
       </c>
       <c r="L10">
-        <v>0.3123611237938697</v>
+        <v>0.3102308687586712</v>
       </c>
       <c r="M10">
-        <v>1171.9466</v>
+        <v>1143.7464</v>
       </c>
       <c r="N10">
-        <v>0.05720021475461843</v>
+        <v>0.05076165580049441</v>
       </c>
       <c r="O10">
-        <v>0.571012765542779</v>
+        <v>0.5747180543691272</v>
       </c>
       <c r="P10">
-        <v>1171.9466</v>
+        <v>1143.7464</v>
       </c>
       <c r="Q10">
-        <v>0.05720021475461843</v>
+        <v>0.05076165580049441</v>
       </c>
       <c r="R10">
-        <v>0.571012765542779</v>
+        <v>0.5747180543691272</v>
       </c>
       <c r="S10">
         <v>0</v>
@@ -1663,61 +1675,308 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>6665.4</v>
+        <v>7132.6</v>
       </c>
       <c r="V10">
-        <v>0.3253239622227103</v>
+        <v>0.3165584487632979</v>
       </c>
       <c r="W10">
-        <v>0.1845301781106426</v>
+        <v>0.1895116748562069</v>
       </c>
       <c r="X10">
-        <v>0.0678828604970885</v>
+        <v>0.07351364360504552</v>
       </c>
       <c r="Y10">
-        <v>0.1166473176135541</v>
+        <v>0.1159980312511614</v>
       </c>
       <c r="Z10">
-        <v>0.244652212280643</v>
+        <v>0.2937574986033136</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.08008145636232357</v>
+        <v>0.07581793452104403</v>
       </c>
       <c r="AC10">
-        <v>-0.08008145636232357</v>
+        <v>-0.07581793452104403</v>
       </c>
       <c r="AD10">
-        <v>18492.5</v>
+        <v>18839.2</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>18492.5</v>
+        <v>18839.2</v>
       </c>
       <c r="AG10">
-        <v>11827.1</v>
+        <v>11706.6</v>
       </c>
       <c r="AH10">
-        <v>0.4743977835355686</v>
+        <v>0.4553732212738906</v>
       </c>
       <c r="AI10">
-        <v>0.6261999979682574</v>
+        <v>0.6422242903358866</v>
       </c>
       <c r="AJ10">
-        <v>0.3659873250071173</v>
+        <v>0.3419153404228598</v>
       </c>
       <c r="AK10">
-        <v>0.517237458398751</v>
+        <v>0.5272839467248004</v>
       </c>
       <c r="AL10">
         <v>0</v>
       </c>
       <c r="AM10">
         <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>African Dawn Capital Limited (JSE:ADW)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D11">
+        <v>0.143</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>-0.895</v>
+      </c>
+      <c r="L11">
+        <v>-1.904255319148936</v>
+      </c>
+      <c r="M11">
+        <v>-0</v>
+      </c>
+      <c r="N11">
+        <v>-0</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>-0</v>
+      </c>
+      <c r="Q11">
+        <v>-0</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>0.11</v>
+      </c>
+      <c r="V11">
+        <v>0.2770780856423174</v>
+      </c>
+      <c r="W11">
+        <v>0.4475</v>
+      </c>
+      <c r="X11">
+        <v>0.1824402202643417</v>
+      </c>
+      <c r="Y11">
+        <v>0.2650597797356583</v>
+      </c>
+      <c r="Z11">
+        <v>0.7366771159874609</v>
+      </c>
+      <c r="AA11">
+        <v>0</v>
+      </c>
+      <c r="AB11">
+        <v>0.07663888802421662</v>
+      </c>
+      <c r="AC11">
+        <v>-0.07663888802421662</v>
+      </c>
+      <c r="AD11">
+        <v>3.08</v>
+      </c>
+      <c r="AE11">
+        <v>0</v>
+      </c>
+      <c r="AF11">
+        <v>3.08</v>
+      </c>
+      <c r="AG11">
+        <v>2.97</v>
+      </c>
+      <c r="AH11">
+        <v>0.8858211101524301</v>
+      </c>
+      <c r="AI11">
+        <v>5.599999999999997</v>
+      </c>
+      <c r="AJ11">
+        <v>0.8820908820908822</v>
+      </c>
+      <c r="AK11">
+        <v>6.749999999999995</v>
+      </c>
+      <c r="AL11">
+        <v>0</v>
+      </c>
+      <c r="AM11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Lesaka Technologies, Inc. (NasdaqGS:LSAK)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D12">
+        <v>-0.0101</v>
+      </c>
+      <c r="G12">
+        <v>0.02948266271092157</v>
+      </c>
+      <c r="H12">
+        <v>0.02855553495271649</v>
+      </c>
+      <c r="I12">
+        <v>-0.004168415304578265</v>
+      </c>
+      <c r="J12">
+        <v>-0.004168415304578265</v>
+      </c>
+      <c r="K12">
+        <v>-30</v>
+      </c>
+      <c r="L12">
+        <v>-0.05562766549230484</v>
+      </c>
+      <c r="M12">
+        <v>1.1</v>
+      </c>
+      <c r="N12">
+        <v>0.005673027333677153</v>
+      </c>
+      <c r="O12">
+        <v>-0.03666666666666667</v>
+      </c>
+      <c r="P12">
+        <v>-0</v>
+      </c>
+      <c r="Q12">
+        <v>-0</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12">
+        <v>1.1</v>
+      </c>
+      <c r="T12">
+        <v>1</v>
+      </c>
+      <c r="U12">
+        <v>35.1</v>
+      </c>
+      <c r="V12">
+        <v>0.1810211449200619</v>
+      </c>
+      <c r="W12">
+        <v>-0.1457017969888295</v>
+      </c>
+      <c r="X12">
+        <v>0.07397351425777443</v>
+      </c>
+      <c r="Y12">
+        <v>-0.2196753112466039</v>
+      </c>
+      <c r="Z12">
+        <v>2.339796483378266</v>
+      </c>
+      <c r="AA12">
+        <v>-0.009753243470912368</v>
+      </c>
+      <c r="AB12">
+        <v>0.0679796776577285</v>
+      </c>
+      <c r="AC12">
+        <v>-0.07773292112864087</v>
+      </c>
+      <c r="AD12">
+        <v>163</v>
+      </c>
+      <c r="AE12">
+        <v>4.790131868795291</v>
+      </c>
+      <c r="AF12">
+        <v>167.7901318687953</v>
+      </c>
+      <c r="AG12">
+        <v>132.6901318687953</v>
+      </c>
+      <c r="AH12">
+        <v>0.4639057499353118</v>
+      </c>
+      <c r="AI12">
+        <v>0.4890555462928957</v>
+      </c>
+      <c r="AJ12">
+        <v>0.4062894708714052</v>
+      </c>
+      <c r="AK12">
+        <v>0.4308259198555157</v>
+      </c>
+      <c r="AL12">
+        <v>19.4</v>
+      </c>
+      <c r="AM12">
+        <v>17.51</v>
+      </c>
+      <c r="AN12">
+        <v>7.335733573357335</v>
+      </c>
+      <c r="AO12">
+        <v>-0.1757731958762887</v>
+      </c>
+      <c r="AP12">
+        <v>5.971653099405729</v>
+      </c>
+      <c r="AQ12">
+        <v>-0.1947458595088521</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/south_africa/south_africa_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/south_africa/south_africa_financial_svcs_non_bank_insurance.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,112 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.058</v>
+        <v>0.0602</v>
       </c>
       <c r="E2">
-        <v>0.051</v>
+        <v>0.05495</v>
       </c>
       <c r="F2">
         <v>0.114</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>0.01349475804698786</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.01127844830923628</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>0.009103749002182531</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>0.006894435955517184</v>
       </c>
       <c r="K2">
-        <v>2175.2</v>
+        <v>3125.962</v>
       </c>
       <c r="L2">
-        <v>0.3127803980213965</v>
+        <v>0.2973433485167989</v>
       </c>
       <c r="M2">
-        <v>1421.1</v>
+        <v>2251.7978</v>
       </c>
       <c r="N2">
-        <v>0.06303868555180475</v>
+        <v>0.07593432305233482</v>
       </c>
       <c r="O2">
-        <v>0.6533192350128724</v>
+        <v>0.7203535423655182</v>
       </c>
       <c r="P2">
-        <v>1297</v>
+        <v>1751.7578</v>
       </c>
       <c r="Q2">
-        <v>0.05753372398894572</v>
+        <v>0.05907215234629296</v>
       </c>
       <c r="R2">
-        <v>0.5962670099301214</v>
+        <v>0.5603899855468493</v>
       </c>
       <c r="S2">
-        <v>124.0999999999999</v>
+        <v>500.0399999999999</v>
       </c>
       <c r="T2">
-        <v>0.08732671873900494</v>
+        <v>0.222062567074184</v>
       </c>
       <c r="U2">
-        <v>6462.5</v>
+        <v>13691.006</v>
       </c>
       <c r="V2">
-        <v>0.2866705406928001</v>
+        <v>0.4616832259608097</v>
       </c>
       <c r="W2">
-        <v>0.2110308028134853</v>
+        <v>0.1146282973621103</v>
       </c>
       <c r="X2">
-        <v>0.07663030540131538</v>
+        <v>0.07163621023456726</v>
       </c>
       <c r="Y2">
-        <v>0.1344004974121699</v>
+        <v>0.04299208712754304</v>
       </c>
       <c r="Z2">
-        <v>0.3011710088691796</v>
+        <v>0.3458583126209722</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>0.05192556059675029</v>
       </c>
       <c r="AB2">
-        <v>0.07682515975052509</v>
+        <v>0.06891601895911723</v>
       </c>
       <c r="AC2">
-        <v>-0.07682515975052509</v>
+        <v>-0.01699045836236694</v>
       </c>
       <c r="AD2">
-        <v>16736.1</v>
+        <v>24119.65</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>7.41275374388058</v>
       </c>
       <c r="AF2">
-        <v>16736.1</v>
+        <v>24127.06275374388</v>
       </c>
       <c r="AG2">
-        <v>10273.6</v>
+        <v>10436.05675374388</v>
       </c>
       <c r="AH2">
-        <v>0.4260783005850395</v>
+        <v>0.4486117794063962</v>
       </c>
       <c r="AI2">
-        <v>0.5838065803426913</v>
+        <v>0.5450188013254107</v>
       </c>
       <c r="AJ2">
-        <v>0.3130582108608674</v>
+        <v>0.2603118012008713</v>
       </c>
       <c r="AK2">
-        <v>0.4626768206731007</v>
+        <v>0.3413007181368611</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>298.302</v>
       </c>
       <c r="AM2">
-        <v>0</v>
+        <v>16.01199999999994</v>
+      </c>
+      <c r="AN2">
+        <v>192.8954734484965</v>
+      </c>
+      <c r="AO2">
+        <v>0.3152845103284591</v>
+      </c>
+      <c r="AP2">
+        <v>83.46174627114425</v>
+      </c>
+      <c r="AQ2">
+        <v>5.873719710217357</v>
       </c>
     </row>
     <row r="3">
@@ -704,120 +716,1135 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>Capital Appreciation Limited (JSE:CTA)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D3">
+        <v>0.166</v>
+      </c>
+      <c r="E3">
+        <v>0.06709999999999999</v>
+      </c>
+      <c r="G3">
+        <v>0.16991643454039</v>
+      </c>
+      <c r="H3">
+        <v>0.16991643454039</v>
+      </c>
+      <c r="I3">
+        <v>0.1559888579387187</v>
+      </c>
+      <c r="J3">
+        <v>0.1101097820743896</v>
+      </c>
+      <c r="K3">
+        <v>9.56</v>
+      </c>
+      <c r="L3">
+        <v>0.1331476323119777</v>
+      </c>
+      <c r="M3">
+        <v>10.51</v>
+      </c>
+      <c r="N3">
+        <v>0.1040594059405941</v>
+      </c>
+      <c r="O3">
+        <v>1.099372384937238</v>
+      </c>
+      <c r="P3">
+        <v>7.3</v>
+      </c>
+      <c r="Q3">
+        <v>0.07227722772277227</v>
+      </c>
+      <c r="R3">
+        <v>0.7635983263598326</v>
+      </c>
+      <c r="S3">
+        <v>3.21</v>
+      </c>
+      <c r="T3">
+        <v>0.3054234062797336</v>
+      </c>
+      <c r="U3">
+        <v>18.9</v>
+      </c>
+      <c r="V3">
+        <v>0.1871287128712871</v>
+      </c>
+      <c r="W3">
+        <v>0.1146282973621103</v>
+      </c>
+      <c r="X3">
+        <v>0.06604233790389463</v>
+      </c>
+      <c r="Y3">
+        <v>0.04858595945821567</v>
+      </c>
+      <c r="Z3">
+        <v>5.47673531655225</v>
+      </c>
+      <c r="AA3">
+        <v>0.6030421321846816</v>
+      </c>
+      <c r="AB3">
+        <v>0.06597632893151063</v>
+      </c>
+      <c r="AC3">
+        <v>0.537065803253171</v>
+      </c>
+      <c r="AD3">
+        <v>1.73</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>1.73</v>
+      </c>
+      <c r="AG3">
+        <v>-17.17</v>
+      </c>
+      <c r="AH3">
+        <v>0.01684026087802979</v>
+      </c>
+      <c r="AI3">
+        <v>0.01853637629915354</v>
+      </c>
+      <c r="AJ3">
+        <v>-0.2048192771084337</v>
+      </c>
+      <c r="AK3">
+        <v>-0.2306865511218595</v>
+      </c>
+      <c r="AL3">
+        <v>0.321</v>
+      </c>
+      <c r="AM3">
+        <v>-2.249</v>
+      </c>
+      <c r="AN3">
+        <v>0.1330769230769231</v>
+      </c>
+      <c r="AO3">
+        <v>34.89096573208722</v>
+      </c>
+      <c r="AP3">
+        <v>-1.320769230769231</v>
+      </c>
+      <c r="AQ3">
+        <v>-4.979991107158738</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>JSE Limited (JSE:JSE)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>0.0624</v>
+      </c>
+      <c r="E4">
+        <v>0.0233</v>
+      </c>
+      <c r="G4">
+        <v>0.453105196451204</v>
+      </c>
+      <c r="H4">
+        <v>0.3086185044359949</v>
+      </c>
+      <c r="I4">
+        <v>0.2775665399239544</v>
+      </c>
+      <c r="J4">
+        <v>0.2011031459640115</v>
+      </c>
+      <c r="K4">
+        <v>45.5</v>
+      </c>
+      <c r="L4">
+        <v>0.288339670468948</v>
+      </c>
+      <c r="M4">
+        <v>43.1</v>
+      </c>
+      <c r="N4">
+        <v>0.0788222384784199</v>
+      </c>
+      <c r="O4">
+        <v>0.9472527472527473</v>
+      </c>
+      <c r="P4">
+        <v>36.1</v>
+      </c>
+      <c r="Q4">
+        <v>0.06602048280907097</v>
+      </c>
+      <c r="R4">
+        <v>0.7934065934065935</v>
+      </c>
+      <c r="S4">
+        <v>7</v>
+      </c>
+      <c r="T4">
+        <v>0.1624129930394431</v>
+      </c>
+      <c r="U4">
+        <v>99.2</v>
+      </c>
+      <c r="V4">
+        <v>0.1814191660570593</v>
+      </c>
+      <c r="W4">
+        <v>0.2119236143455985</v>
+      </c>
+      <c r="X4">
+        <v>0.0659324799336819</v>
+      </c>
+      <c r="Y4">
+        <v>0.1459911344119166</v>
+      </c>
+      <c r="Z4">
+        <v>1.283448556323709</v>
+      </c>
+      <c r="AA4">
+        <v>0.2581055423596667</v>
+      </c>
+      <c r="AB4">
+        <v>0.0658719501201243</v>
+      </c>
+      <c r="AC4">
+        <v>0.1922335922395424</v>
+      </c>
+      <c r="AD4">
+        <v>5.25</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>5.25</v>
+      </c>
+      <c r="AG4">
+        <v>-93.95</v>
+      </c>
+      <c r="AH4">
+        <v>0.009510008151435559</v>
+      </c>
+      <c r="AI4">
+        <v>0.0226537216828479</v>
+      </c>
+      <c r="AJ4">
+        <v>-0.2074638401236613</v>
+      </c>
+      <c r="AK4">
+        <v>-0.7087891361750283</v>
+      </c>
+      <c r="AL4">
+        <v>258.7</v>
+      </c>
+      <c r="AM4">
+        <v>-17.80000000000001</v>
+      </c>
+      <c r="AN4">
+        <v>0.109375</v>
+      </c>
+      <c r="AO4">
+        <v>0.1693080788558176</v>
+      </c>
+      <c r="AP4">
+        <v>-1.957291666666667</v>
+      </c>
+      <c r="AQ4">
+        <v>-2.460674157303369</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Vunani Limited (JSE:VUN)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D5">
+        <v>0.0809</v>
+      </c>
+      <c r="G5">
+        <v>0.09494680851063829</v>
+      </c>
+      <c r="H5">
+        <v>0.09494680851063829</v>
+      </c>
+      <c r="I5">
+        <v>0.03430851063829787</v>
+      </c>
+      <c r="J5">
+        <v>0.01715425531914894</v>
+      </c>
+      <c r="K5">
+        <v>-0.211</v>
+      </c>
+      <c r="L5">
+        <v>-0.005611702127659574</v>
+      </c>
+      <c r="M5">
+        <v>1.68</v>
+      </c>
+      <c r="N5">
+        <v>0.09940828402366866</v>
+      </c>
+      <c r="O5">
+        <v>-7.962085308056873</v>
+      </c>
+      <c r="P5">
+        <v>1.61</v>
+      </c>
+      <c r="Q5">
+        <v>0.09526627218934913</v>
+      </c>
+      <c r="R5">
+        <v>-7.630331753554503</v>
+      </c>
+      <c r="S5">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="T5">
+        <v>0.0416666666666667</v>
+      </c>
+      <c r="U5">
+        <v>10.1</v>
+      </c>
+      <c r="V5">
+        <v>0.5976331360946746</v>
+      </c>
+      <c r="W5">
+        <v>-0.01165745856353591</v>
+      </c>
+      <c r="X5">
+        <v>0.06948845558553569</v>
+      </c>
+      <c r="Y5">
+        <v>-0.0811459141490716</v>
+      </c>
+      <c r="Z5">
+        <v>6.394557823129248</v>
+      </c>
+      <c r="AA5">
+        <v>0.1096938775510203</v>
+      </c>
+      <c r="AB5">
+        <v>0.06836877895802655</v>
+      </c>
+      <c r="AC5">
+        <v>0.0413250985929938</v>
+      </c>
+      <c r="AD5">
+        <v>4.28</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>4.28</v>
+      </c>
+      <c r="AG5">
+        <v>-5.819999999999999</v>
+      </c>
+      <c r="AH5">
+        <v>0.2020774315391879</v>
+      </c>
+      <c r="AI5">
+        <v>0.1610233258088788</v>
+      </c>
+      <c r="AJ5">
+        <v>-0.5252707581227437</v>
+      </c>
+      <c r="AK5">
+        <v>-0.3531553398058252</v>
+      </c>
+      <c r="AL5">
+        <v>0.881</v>
+      </c>
+      <c r="AM5">
+        <v>0.09099999999999997</v>
+      </c>
+      <c r="AN5">
+        <v>1.945454545454545</v>
+      </c>
+      <c r="AO5">
+        <v>1.464245175936436</v>
+      </c>
+      <c r="AP5">
+        <v>-2.645454545454545</v>
+      </c>
+      <c r="AQ5">
+        <v>14.17582417582418</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Finbond Group Limited (JSE:FGL)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D6">
+        <v>-0.08939999999999999</v>
+      </c>
+      <c r="G6">
+        <v>0.2658643326039387</v>
+      </c>
+      <c r="H6">
+        <v>0.2658643326039387</v>
+      </c>
+      <c r="I6">
+        <v>0.2822757111597374</v>
+      </c>
+      <c r="J6">
+        <v>0.1411378555798687</v>
+      </c>
+      <c r="K6">
+        <v>0.051</v>
+      </c>
+      <c r="L6">
+        <v>0.0005579868708971553</v>
+      </c>
+      <c r="M6">
+        <v>5.59</v>
+      </c>
+      <c r="N6">
+        <v>0.3560509554140128</v>
+      </c>
+      <c r="O6">
+        <v>109.6078431372549</v>
+      </c>
+      <c r="P6">
+        <v>-0</v>
+      </c>
+      <c r="Q6">
+        <v>-0</v>
+      </c>
+      <c r="R6">
+        <v>-0</v>
+      </c>
+      <c r="S6">
+        <v>5.59</v>
+      </c>
+      <c r="T6">
+        <v>1</v>
+      </c>
+      <c r="U6">
+        <v>32.5</v>
+      </c>
+      <c r="V6">
+        <v>2.070063694267516</v>
+      </c>
+      <c r="W6">
+        <v>0.001175115207373272</v>
+      </c>
+      <c r="X6">
+        <v>0.2172210674185493</v>
+      </c>
+      <c r="Y6">
+        <v>-0.2160459522111761</v>
+      </c>
+      <c r="Z6">
+        <v>0.7047031611410948</v>
+      </c>
+      <c r="AA6">
+        <v>0.09946029298380878</v>
+      </c>
+      <c r="AB6">
+        <v>0.08161599171756642</v>
+      </c>
+      <c r="AC6">
+        <v>0.01784430126624235</v>
+      </c>
+      <c r="AD6">
+        <v>162.9</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>162.9</v>
+      </c>
+      <c r="AG6">
+        <v>130.4</v>
+      </c>
+      <c r="AH6">
+        <v>0.9120940649496081</v>
+      </c>
+      <c r="AI6">
+        <v>0.8202416918429002</v>
+      </c>
+      <c r="AJ6">
+        <v>0.8925393566050651</v>
+      </c>
+      <c r="AK6">
+        <v>0.7850692354003611</v>
+      </c>
+      <c r="AL6">
+        <v>19.3</v>
+      </c>
+      <c r="AM6">
+        <v>19.3</v>
+      </c>
+      <c r="AN6">
+        <v>6.011070110701107</v>
+      </c>
+      <c r="AO6">
+        <v>1.336787564766839</v>
+      </c>
+      <c r="AP6">
+        <v>4.81180811808118</v>
+      </c>
+      <c r="AQ6">
+        <v>1.336787564766839</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Lesaka Technologies, Inc. (NasdaqGS:LSAK)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D7">
+        <v>0.356</v>
+      </c>
+      <c r="G7">
+        <v>0.05281506013595956</v>
+      </c>
+      <c r="H7">
+        <v>0.05194352449015165</v>
+      </c>
+      <c r="I7">
+        <v>0.01606667117173415</v>
+      </c>
+      <c r="J7">
+        <v>0.01606667117173415</v>
+      </c>
+      <c r="K7">
+        <v>-16.3</v>
+      </c>
+      <c r="L7">
+        <v>-0.02841206205333798</v>
+      </c>
+      <c r="M7">
+        <v>1.5</v>
+      </c>
+      <c r="N7">
+        <v>0.003622313450857281</v>
+      </c>
+      <c r="O7">
+        <v>-0.09202453987730061</v>
+      </c>
+      <c r="P7">
+        <v>-0</v>
+      </c>
+      <c r="Q7">
+        <v>-0</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>1.5</v>
+      </c>
+      <c r="T7">
+        <v>1</v>
+      </c>
+      <c r="U7">
+        <v>49.7</v>
+      </c>
+      <c r="V7">
+        <v>0.1200193190050712</v>
+      </c>
+      <c r="W7">
+        <v>-0.09298345693097547</v>
+      </c>
+      <c r="X7">
+        <v>0.07163621023456726</v>
+      </c>
+      <c r="Y7">
+        <v>-0.1646196671655427</v>
+      </c>
+      <c r="Z7">
+        <v>3.231880458728883</v>
+      </c>
+      <c r="AA7">
+        <v>0.05192556059675029</v>
+      </c>
+      <c r="AB7">
+        <v>0.06891601895911723</v>
+      </c>
+      <c r="AC7">
+        <v>-0.01699045836236694</v>
+      </c>
+      <c r="AD7">
+        <v>158.4</v>
+      </c>
+      <c r="AE7">
+        <v>7.41275374388058</v>
+      </c>
+      <c r="AF7">
+        <v>165.8127537438806</v>
+      </c>
+      <c r="AG7">
+        <v>116.1127537438806</v>
+      </c>
+      <c r="AH7">
+        <v>0.2859270686381767</v>
+      </c>
+      <c r="AI7">
+        <v>0.473733462481807</v>
+      </c>
+      <c r="AJ7">
+        <v>0.2189927588953639</v>
+      </c>
+      <c r="AK7">
+        <v>0.3866394360424215</v>
+      </c>
+      <c r="AL7">
+        <v>19.1</v>
+      </c>
+      <c r="AM7">
+        <v>16.67</v>
+      </c>
+      <c r="AN7">
+        <v>4.559585492227979</v>
+      </c>
+      <c r="AO7">
+        <v>0.3958115183246073</v>
+      </c>
+      <c r="AP7">
+        <v>3.342336031775492</v>
+      </c>
+      <c r="AQ7">
+        <v>0.4535092981403718</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>RMB Holdings Limited (JSE:RMH)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>1.09181141439206</v>
+      </c>
+      <c r="J8">
+        <v>0.8915830235173913</v>
+      </c>
+      <c r="K8">
+        <v>4.72</v>
+      </c>
+      <c r="L8">
+        <v>1.1712158808933</v>
+      </c>
+      <c r="M8">
+        <v>2.97</v>
+      </c>
+      <c r="N8">
+        <v>0.0939873417721519</v>
+      </c>
+      <c r="O8">
+        <v>0.6292372881355933</v>
+      </c>
+      <c r="P8">
+        <v>-0</v>
+      </c>
+      <c r="Q8">
+        <v>-0</v>
+      </c>
+      <c r="R8">
+        <v>-0</v>
+      </c>
+      <c r="S8">
+        <v>2.97</v>
+      </c>
+      <c r="T8">
+        <v>1</v>
+      </c>
+      <c r="U8">
+        <v>5.08</v>
+      </c>
+      <c r="V8">
+        <v>0.1607594936708861</v>
+      </c>
+      <c r="W8">
+        <v>0.05907384230287859</v>
+      </c>
+      <c r="X8">
+        <v>0.06579235429753466</v>
+      </c>
+      <c r="Y8">
+        <v>-0.006718511994656069</v>
+      </c>
+      <c r="Z8">
+        <v>0.05402869017294543</v>
+      </c>
+      <c r="AA8">
+        <v>0.04817106294107905</v>
+      </c>
+      <c r="AB8">
+        <v>0.06579235429753466</v>
+      </c>
+      <c r="AC8">
+        <v>-0.01762129135645561</v>
+      </c>
+      <c r="AD8">
+        <v>0</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>0</v>
+      </c>
+      <c r="AG8">
+        <v>-5.08</v>
+      </c>
+      <c r="AH8">
+        <v>0</v>
+      </c>
+      <c r="AI8">
+        <v>0</v>
+      </c>
+      <c r="AJ8">
+        <v>-0.191553544494721</v>
+      </c>
+      <c r="AK8">
+        <v>-0.09879424348502527</v>
+      </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Investec Group (JSE:INL)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D9">
+        <v>0.0559</v>
+      </c>
+      <c r="E9">
+        <v>0.05889999999999999</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>908.3</v>
+      </c>
+      <c r="L9">
+        <v>0.3463885287163451</v>
+      </c>
+      <c r="M9">
+        <v>765.3478</v>
+      </c>
+      <c r="N9">
+        <v>0.1278862079336965</v>
+      </c>
+      <c r="O9">
+        <v>0.8426156556203898</v>
+      </c>
+      <c r="P9">
+        <v>409.7478</v>
+      </c>
+      <c r="Q9">
+        <v>0.06846703204892557</v>
+      </c>
+      <c r="R9">
+        <v>0.4511150500935814</v>
+      </c>
+      <c r="S9">
+        <v>355.6</v>
+      </c>
+      <c r="T9">
+        <v>0.4646253637888552</v>
+      </c>
+      <c r="U9">
+        <v>7013</v>
+      </c>
+      <c r="V9">
+        <v>1.171841058717374</v>
+      </c>
+      <c r="W9">
+        <v>0.1457500922672058</v>
+      </c>
+      <c r="X9">
+        <v>0.08297833940296222</v>
+      </c>
+      <c r="Y9">
+        <v>0.06277175286424362</v>
+      </c>
+      <c r="Z9">
+        <v>0.3866753177809892</v>
+      </c>
+      <c r="AA9">
+        <v>0</v>
+      </c>
+      <c r="AB9">
+        <v>0.07031845702725176</v>
+      </c>
+      <c r="AC9">
+        <v>-0.07031845702725176</v>
+      </c>
+      <c r="AD9">
+        <v>7047.3</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>7047.3</v>
+      </c>
+      <c r="AG9">
+        <v>34.30000000000018</v>
+      </c>
+      <c r="AH9">
+        <v>0.5407730261895809</v>
+      </c>
+      <c r="AI9">
+        <v>0.4812348916294505</v>
+      </c>
+      <c r="AJ9">
+        <v>0.005698715712173351</v>
+      </c>
+      <c r="AK9">
+        <v>0.004494705944019313</v>
+      </c>
+      <c r="AL9">
+        <v>0</v>
+      </c>
+      <c r="AM9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
           <t>FirstRand Limited (JSE:FSR)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D3">
+      <c r="D10">
         <v>0.058</v>
       </c>
-      <c r="E3">
+      <c r="E10">
         <v>0.051</v>
       </c>
-      <c r="F3">
+      <c r="F10">
         <v>0.114</v>
       </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3">
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
         <v>2175.2</v>
       </c>
-      <c r="L3">
+      <c r="L10">
         <v>0.3127803980213965</v>
       </c>
-      <c r="M3">
+      <c r="M10">
         <v>1421.1</v>
       </c>
-      <c r="N3">
+      <c r="N10">
         <v>0.06303868555180475</v>
       </c>
-      <c r="O3">
+      <c r="O10">
         <v>0.6533192350128724</v>
       </c>
-      <c r="P3">
+      <c r="P10">
         <v>1297</v>
       </c>
-      <c r="Q3">
+      <c r="Q10">
         <v>0.05753372398894572</v>
       </c>
-      <c r="R3">
+      <c r="R10">
         <v>0.5962670099301214</v>
       </c>
-      <c r="S3">
+      <c r="S10">
         <v>124.0999999999999</v>
       </c>
-      <c r="T3">
+      <c r="T10">
         <v>0.08732671873900494</v>
       </c>
-      <c r="U3">
+      <c r="U10">
         <v>6462.5</v>
       </c>
-      <c r="V3">
+      <c r="V10">
         <v>0.2866705406928001</v>
       </c>
-      <c r="W3">
+      <c r="W10">
         <v>0.2110308028134853</v>
       </c>
-      <c r="X3">
-        <v>0.07663030540131538</v>
-      </c>
-      <c r="Y3">
-        <v>0.1344004974121699</v>
-      </c>
-      <c r="Z3">
+      <c r="X10">
+        <v>0.07662722096541594</v>
+      </c>
+      <c r="Y10">
+        <v>0.1344035818480694</v>
+      </c>
+      <c r="Z10">
         <v>0.3011710088691796</v>
       </c>
-      <c r="AA3">
-        <v>0</v>
-      </c>
-      <c r="AB3">
-        <v>0.07682515975052509</v>
-      </c>
-      <c r="AC3">
-        <v>-0.07682515975052509</v>
-      </c>
-      <c r="AD3">
+      <c r="AA10">
+        <v>0</v>
+      </c>
+      <c r="AB10">
+        <v>0.07682338952583194</v>
+      </c>
+      <c r="AC10">
+        <v>-0.07682338952583194</v>
+      </c>
+      <c r="AD10">
         <v>16736.1</v>
       </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3">
+      <c r="AE10">
+        <v>0</v>
+      </c>
+      <c r="AF10">
         <v>16736.1</v>
       </c>
-      <c r="AG3">
+      <c r="AG10">
         <v>10273.6</v>
       </c>
-      <c r="AH3">
+      <c r="AH10">
         <v>0.4260783005850395</v>
       </c>
-      <c r="AI3">
+      <c r="AI10">
         <v>0.5838065803426913</v>
       </c>
-      <c r="AJ3">
+      <c r="AJ10">
         <v>0.3130582108608674</v>
       </c>
-      <c r="AK3">
+      <c r="AK10">
         <v>0.4626768206731007</v>
       </c>
-      <c r="AL3">
-        <v>0</v>
-      </c>
-      <c r="AM3">
+      <c r="AL10">
+        <v>0</v>
+      </c>
+      <c r="AM10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>African Dawn Capital Limited (JSE:ADW)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D11">
+        <v>-0.408</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>-0.858</v>
+      </c>
+      <c r="L11">
+        <v>-20.92682926829268</v>
+      </c>
+      <c r="M11">
+        <v>-0</v>
+      </c>
+      <c r="N11">
+        <v>-0</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>-0</v>
+      </c>
+      <c r="Q11">
+        <v>-0</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>0.026</v>
+      </c>
+      <c r="V11">
+        <v>0.04770642201834862</v>
+      </c>
+      <c r="W11">
+        <v>0.3391304347826087</v>
+      </c>
+      <c r="X11">
+        <v>0.1646059410338083</v>
+      </c>
+      <c r="Y11">
+        <v>0.1745244937488004</v>
+      </c>
+      <c r="Z11">
+        <v>0.09903381642512071</v>
+      </c>
+      <c r="AA11">
+        <v>0</v>
+      </c>
+      <c r="AB11">
+        <v>0.07690129338993418</v>
+      </c>
+      <c r="AC11">
+        <v>-0.07690129338993418</v>
+      </c>
+      <c r="AD11">
+        <v>3.69</v>
+      </c>
+      <c r="AE11">
+        <v>0</v>
+      </c>
+      <c r="AF11">
+        <v>3.69</v>
+      </c>
+      <c r="AG11">
+        <v>3.664</v>
+      </c>
+      <c r="AH11">
+        <v>0.871310507674144</v>
+      </c>
+      <c r="AI11">
+        <v>26.35714285714283</v>
+      </c>
+      <c r="AJ11">
+        <v>0.8705155618911855</v>
+      </c>
+      <c r="AK11">
+        <v>32.14035087719289</v>
+      </c>
+      <c r="AL11">
+        <v>0</v>
+      </c>
+      <c r="AM11">
         <v>0</v>
       </c>
     </row>
